--- a/data/trans_orig/IP12-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP12-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7520</t>
+          <t>7086</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17961</t>
+          <t>18513</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7126</t>
+          <t>6916</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17590</t>
+          <t>18476</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17776</t>
+          <t>16494</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32237</t>
+          <t>32305</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>120765</t>
+          <t>120213</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>131206</t>
+          <t>131640</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>135487</t>
+          <t>134601</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>145951</t>
+          <t>146161</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>259566</t>
+          <t>259498</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>274027</t>
+          <t>275309</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,35%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7765</t>
+          <t>7572</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18171</t>
+          <t>17419</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11390</t>
+          <t>10791</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24660</t>
+          <t>23915</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21719</t>
+          <t>21371</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37884</t>
+          <t>38522</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>176992</t>
+          <t>177744</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>187398</t>
+          <t>187591</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>187482</t>
+          <t>188227</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>200752</t>
+          <t>201351</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>369421</t>
+          <t>368783</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>385586</t>
+          <t>385934</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,75%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7940</t>
+          <t>8606</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18782</t>
+          <t>18886</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4913</t>
+          <t>4589</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13882</t>
+          <t>13978</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14830</t>
+          <t>14668</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28340</t>
+          <t>28351</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>119035</t>
+          <t>118931</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>129877</t>
+          <t>129211</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>135775</t>
+          <t>135679</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>144744</t>
+          <t>145068</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>259134</t>
+          <t>259123</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>272644</t>
+          <t>272806</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,9%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3597</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12805</t>
+          <t>12437</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6212</t>
+          <t>5929</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16495</t>
+          <t>16052</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11306</t>
+          <t>11912</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25785</t>
+          <t>25882</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>196510</t>
+          <t>196878</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>205718</t>
+          <t>206313</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>191329</t>
+          <t>191772</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>201612</t>
+          <t>201895</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>391354</t>
+          <t>391257</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>405833</t>
+          <t>405227</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34289</t>
+          <t>34365</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55048</t>
+          <t>55556</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38030</t>
+          <t>37521</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57921</t>
+          <t>58690</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>76515</t>
+          <t>78269</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>107244</t>
+          <t>107397</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>625973</t>
+          <t>625465</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>646732</t>
+          <t>646656</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>664779</t>
+          <t>664010</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>684670</t>
+          <t>685179</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1296477</t>
+          <t>1296324</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1327206</t>
+          <t>1325452</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,42%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11036</t>
+          <t>11667</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24344</t>
+          <t>24611</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5800</t>
+          <t>5969</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16559</t>
+          <t>16812</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19773</t>
+          <t>19452</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36018</t>
+          <t>37313</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,69%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>115013</t>
+          <t>114746</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>128321</t>
+          <t>127690</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>138125</t>
+          <t>137872</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>148884</t>
+          <t>148715</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>258023</t>
+          <t>256728</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>274268</t>
+          <t>274589</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,38%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12855</t>
+          <t>13187</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26255</t>
+          <t>27523</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8890</t>
+          <t>8531</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21623</t>
+          <t>21348</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25254</t>
+          <t>25509</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44144</t>
+          <t>43019</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>180103</t>
+          <t>178835</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>193503</t>
+          <t>193171</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>202212</t>
+          <t>202487</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>214945</t>
+          <t>215304</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>386049</t>
+          <t>387174</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>404939</t>
+          <t>404684</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,07%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5730</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15690</t>
+          <t>15365</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12410</t>
+          <t>12733</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25532</t>
+          <t>25416</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19837</t>
+          <t>20883</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36492</t>
+          <t>36498</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>139686</t>
+          <t>140011</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>149646</t>
+          <t>149875</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141060</t>
+          <t>141176</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>154182</t>
+          <t>153859</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>285476</t>
+          <t>285470</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>302131</t>
+          <t>301085</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,51%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10084</t>
+          <t>10219</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22763</t>
+          <t>23630</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14370</t>
+          <t>14631</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30541</t>
+          <t>29585</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28120</t>
+          <t>27813</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46799</t>
+          <t>48487</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>187537</t>
+          <t>186670</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>200216</t>
+          <t>200081</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>177855</t>
+          <t>178811</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>194026</t>
+          <t>193765</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>371897</t>
+          <t>370209</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>390576</t>
+          <t>390883</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,36%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50187</t>
+          <t>49428</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>74651</t>
+          <t>74848</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51223</t>
+          <t>52770</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>76314</t>
+          <t>77354</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>107969</t>
+          <t>107955</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>145150</t>
+          <t>144490</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>636740</t>
+          <t>636543</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>661204</t>
+          <t>661963</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>677193</t>
+          <t>676153</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>702284</t>
+          <t>700737</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1319748</t>
+          <t>1320408</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1356929</t>
+          <t>1356943</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4577</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15379</t>
+          <t>15417</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3424</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13122</t>
+          <t>14286</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10469</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24377</t>
+          <t>23684</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>118328</t>
+          <t>118290</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>129130</t>
+          <t>128878</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>134954</t>
+          <t>133790</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>144652</t>
+          <t>144552</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>257406</t>
+          <t>258099</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>271314</t>
+          <t>271630</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,4%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14459</t>
+          <t>14756</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27492</t>
+          <t>27852</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10651</t>
+          <t>10562</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22802</t>
+          <t>23830</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28385</t>
+          <t>28533</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46664</t>
+          <t>46336</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>179138</t>
+          <t>178778</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>192171</t>
+          <t>191874</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>201557</t>
+          <t>200529</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>213708</t>
+          <t>213797</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>384325</t>
+          <t>384653</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>402604</t>
+          <t>402456</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,38%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7607</t>
+          <t>7786</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18253</t>
+          <t>18956</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9955</t>
+          <t>10750</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22985</t>
+          <t>23295</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20886</t>
+          <t>20437</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37434</t>
+          <t>36836</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,42%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>137744</t>
+          <t>137041</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>148390</t>
+          <t>148211</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>143688</t>
+          <t>143378</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>156718</t>
+          <t>155923</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>285236</t>
+          <t>285834</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>301784</t>
+          <t>302233</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,67%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8886</t>
+          <t>9170</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21798</t>
+          <t>21315</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5433</t>
+          <t>4955</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15495</t>
+          <t>15471</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16595</t>
+          <t>16563</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32983</t>
+          <t>32377</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>185622</t>
+          <t>186105</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>198534</t>
+          <t>198250</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>190241</t>
+          <t>190265</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>200303</t>
+          <t>200781</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>380173</t>
+          <t>380779</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>396561</t>
+          <t>396593</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,99%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44576</t>
+          <t>44619</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>67704</t>
+          <t>68026</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38826</t>
+          <t>38294</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61026</t>
+          <t>60359</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>90269</t>
+          <t>89092</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>121541</t>
+          <t>121457</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>636050</t>
+          <t>635728</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>659178</t>
+          <t>659135</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>683818</t>
+          <t>684485</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>706018</t>
+          <t>706550</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1327057</t>
+          <t>1327141</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1358329</t>
+          <t>1359506</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,85%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5028</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15309</t>
+          <t>14408</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>4888</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15851</t>
+          <t>15693</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11769</t>
+          <t>11894</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25201</t>
+          <t>25600</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>101971</t>
+          <t>102872</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>112252</t>
+          <t>111991</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>124561</t>
+          <t>124719</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>135476</t>
+          <t>135524</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>232492</t>
+          <t>232093</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>245924</t>
+          <t>245799</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8486</t>
+          <t>8749</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20134</t>
+          <t>20346</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11172</t>
+          <t>11141</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25214</t>
+          <t>25084</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22589</t>
+          <t>23044</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40673</t>
+          <t>41406</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>170378</t>
+          <t>170166</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>182026</t>
+          <t>181763</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>229821</t>
+          <t>229951</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>243863</t>
+          <t>243894</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>404875</t>
+          <t>404142</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>422959</t>
+          <t>422504</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,83%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8055</t>
+          <t>8279</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21653</t>
+          <t>22488</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10107</t>
+          <t>9172</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26905</t>
+          <t>25506</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21656</t>
+          <t>21048</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42896</t>
+          <t>43627</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>167932</t>
+          <t>167097</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>181530</t>
+          <t>181306</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>158381</t>
+          <t>159780</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>175179</t>
+          <t>176114</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>331975</t>
+          <t>331244</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>353215</t>
+          <t>353823</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5881</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15606</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10552</t>
+          <t>10961</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25125</t>
+          <t>24967</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19186</t>
+          <t>19742</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36636</t>
+          <t>36971</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>152356</t>
+          <t>151911</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>162081</t>
+          <t>161963</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>156113</t>
+          <t>156271</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>170686</t>
+          <t>170277</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>312565</t>
+          <t>312230</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>330015</t>
+          <t>329459</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,35%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35978</t>
+          <t>37016</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59317</t>
+          <t>58539</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47607</t>
+          <t>45885</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74856</t>
+          <t>72733</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>89665</t>
+          <t>90023</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>127135</t>
+          <t>125932</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>606023</t>
+          <t>606801</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>629362</t>
+          <t>628324</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>687116</t>
+          <t>689239</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>714365</t>
+          <t>716087</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1300177</t>
+          <t>1301380</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1337647</t>
+          <t>1337289</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,69%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP12-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP12-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -728,67 +728,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>11787</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7072</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>17641</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,62%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>11,52%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>12241</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7086</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>18513</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>7777</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>18905</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>8,82%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,11%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13,35%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>11787</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>6916</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>18476</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,7%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16494</t>
+          <t>16987</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32305</t>
+          <t>32361</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>141290</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>135436</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>146005</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>92,3%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>88,48%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>95,38%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>126485</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>120213</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>131640</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>119821</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>130949</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>91,18%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>86,65%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>94,89%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>141290</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>134601</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>146161</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>92,3%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>259498</t>
+          <t>259442</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>275309</t>
+          <t>274816</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,18%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16832</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11380</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>24304</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,93%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,36%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>11,46%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>12094</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7572</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>17419</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>6863</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>17587</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>6,2%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,88%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,93%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>16832</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>10791</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>23915</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>7,93%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21371</t>
+          <t>21330</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38522</t>
+          <t>37202</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>195310</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>187838</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>200762</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,07%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>88,54%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,64%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>292</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>183069</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>177744</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>187591</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>177576</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>188300</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>93,8%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,07%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,12%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>195310</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>188227</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>201351</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>92,07%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>368783</t>
+          <t>370103</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>385934</t>
+          <t>385975</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,76%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>312</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8278</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4519</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13756</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,53%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,02%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9,19%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>12697</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8606</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18886</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>8225</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>18991</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>9,21%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,24%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13,7%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>8278</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>4589</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>13978</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,53%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14668</t>
+          <t>14315</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28351</t>
+          <t>29592</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>141379</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>135901</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>145138</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,47%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>90,81%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,98%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>125120</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>118931</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>129211</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>118826</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>129592</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>90,79%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>86,3%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>93,76%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>141379</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>135679</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>145068</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,47%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>259123</t>
+          <t>257882</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>272806</t>
+          <t>273159</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>95,02%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10495</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6474</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>16685</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,05%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,12%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,03%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>6845</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3002</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>12437</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2992</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>12208</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,27%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>1,43%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,94%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>10495</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>5929</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>16052</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,05%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11912</t>
+          <t>11491</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25882</t>
+          <t>24729</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -1865,74 +1865,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>197329</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>191139</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>201350</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>94,95%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,97%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,88%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>265</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>202470</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>196878</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>206313</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>197107</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>206323</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,73%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>94,06%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>94,17%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>98,57%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>197329</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>191772</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>201895</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>94,95%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>92,28%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>97,15%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>555</t>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>391257</t>
+          <t>392410</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>405227</t>
+          <t>405648</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,25%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>47392</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>37145</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>58298</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,56%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5,14%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,07%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>43878</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>34365</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>55556</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>34308</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>55512</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>6,44%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,05%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>8,16%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>47392</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>37521</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>58690</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>6,56%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>78269</t>
+          <t>76421</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>107397</t>
+          <t>106506</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>675308</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>664402</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>685555</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>93,44%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>91,93%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>94,86%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>951</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>637143</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>625465</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>646656</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>625509</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>646713</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>93,56%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>91,84%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>94,95%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1015</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>675308</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>664010</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>685179</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>93,44%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1296324</t>
+          <t>1297215</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1325452</t>
+          <t>1327300</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,56%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,107 +2670,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10211</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5459</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>15909</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6,6%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,53%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10,28%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>17142</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>11667</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>24611</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>11502</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>24974</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>12,3%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8,37%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>17,66%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>10211</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>5969</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>16812</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>8,25%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>17,92%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>27354</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>19413</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>37478</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>9,3%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>6,6%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>3,86%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>10,87%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>27354</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>19452</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>37313</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>9,3%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>6,62%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,75%</t>
         </is>
       </c>
     </row>
@@ -2783,107 +2783,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>144473</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>138775</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>149225</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>93,4%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>89,72%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,47%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>122215</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>114746</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>127690</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>114383</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>127855</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>87,7%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>82,34%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>91,63%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>144473</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>137872</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>148715</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>82,08%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>91,75%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>266687</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>256563</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>274628</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>90,7%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>87,25%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
         <is>
           <t>93,4%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>89,13%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>96,14%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>363</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>266687</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>256728</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>274589</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>90,7%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>87,31%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>93,38%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>139357</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>139357</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>139357</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>14126</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8632</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>21435</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,31%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,86%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,58%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>19183</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>13187</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>27523</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>13640</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>27400</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>9,3%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,39%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>13,34%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>14126</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>8531</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>21348</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,31%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25509</t>
+          <t>24363</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43019</t>
+          <t>42771</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>209709</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>202400</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>215203</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>93,69%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>90,42%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,14%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>290</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>187175</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>178835</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>193171</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>178958</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>192718</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>90,7%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>86,66%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>93,61%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>209709</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>202487</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>215304</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>93,69%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>387174</t>
+          <t>387422</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>404684</t>
+          <t>405830</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,34%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>223835</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>223835</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>223835</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>319</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>206358</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>206358</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>206358</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>223835</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>223835</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>223835</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>18117</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12628</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>25828</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10,88%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7,58%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>15,5%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>9416</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5501</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>15365</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5627</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>15190</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>6,06%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,89%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>18117</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>12733</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>25416</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>10,88%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20883</t>
+          <t>19862</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36498</t>
+          <t>36989</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>148475</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>140764</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>153964</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>89,12%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>84,5%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>92,42%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>145960</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>140011</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>149875</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>140186</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>149749</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>93,94%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>90,11%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,46%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>148475</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>141176</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>153859</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>89,12%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>285470</t>
+          <t>284979</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>301085</t>
+          <t>302106</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,83%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166592</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166592</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166592</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>166592</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>166592</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>166592</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>21106</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>14601</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>29557</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>10,13%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,01%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>14,18%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>15551</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>10219</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>23630</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>10091</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>23285</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>7,39%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,86%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>11,24%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>21106</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>14631</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>29585</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>10,13%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27813</t>
+          <t>27891</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48487</t>
+          <t>47872</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>187290</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>178839</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>193795</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>89,87%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>85,82%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>92,99%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>194749</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>186670</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>200081</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>187015</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>200209</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>92,61%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>88,76%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,14%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>187290</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>178811</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>193765</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>89,87%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>370209</t>
+          <t>370824</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>390883</t>
+          <t>390805</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,34%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>208396</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>208396</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>208396</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>208396</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>208396</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>208396</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4047,67 +4047,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>63560</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>51375</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>77387</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>8,44%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>6,82%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>10,27%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>61292</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>49428</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>74848</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>50093</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>73802</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>8,62%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>6,95%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>10,52%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>63560</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>52770</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>77354</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>8,44%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>107955</t>
+          <t>109361</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>144490</t>
+          <t>146480</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>986</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>689947</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>676120</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>702132</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>91,56%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>89,73%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>93,18%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>937</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>650099</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>636543</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>661963</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>637589</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>661298</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>91,38%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>89,48%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>93,05%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>986</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>689947</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>676153</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>700737</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>91,56%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1320408</t>
+          <t>1318418</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1356943</t>
+          <t>1355537</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,53%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1074</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>753507</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>753507</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>753507</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1025</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>711391</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>711391</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>711391</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1074</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>753507</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>753507</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>753507</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7118</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3318</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>13198</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,91%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>8872</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4829</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>15417</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4710</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>14406</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>6,64%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,61%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,53%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>7118</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3524</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>14286</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,81%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>10245</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23684</t>
+          <t>23831</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>140958</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>134878</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>144758</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,19%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>91,09%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,76%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>124835</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>118290</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>128878</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>119301</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>128997</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>93,36%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>88,47%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,39%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>140958</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>133790</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>144552</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,19%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>258099</t>
+          <t>257952</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>271630</t>
+          <t>271538</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,36%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16181</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>23793</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,21%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,59%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10,6%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>20274</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>14756</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>27852</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>14780</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>27021</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>9,81%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7,14%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>13,48%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>16181</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>10562</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>23830</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>7,21%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28533</t>
+          <t>28221</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46336</t>
+          <t>46639</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>208178</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>200566</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>214056</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,79%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>89,4%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,41%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>300</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>186356</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>178778</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>191874</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>179609</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>191850</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>90,19%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>86,52%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>92,86%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>208178</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>200529</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>213797</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>92,79%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>384653</t>
+          <t>384350</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>402456</t>
+          <t>402768</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,45%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>333</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>206630</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>206630</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>206630</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15943</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10433</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>22825</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9,57%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,26%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13,69%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>12193</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7786</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18956</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7898</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>18323</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>7,82%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,99%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,15%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>15943</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>10750</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>23295</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>9,57%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20437</t>
+          <t>21241</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36836</t>
+          <t>37541</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>150730</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>143848</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>156240</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>90,43%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>86,31%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>93,74%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>143804</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>137041</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>148211</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>137674</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>148099</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>92,18%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>87,85%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>95,01%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>150730</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>143378</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>155923</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>90,43%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>285834</t>
+          <t>285129</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>302233</t>
+          <t>301429</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,42%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9240</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4998</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>14555</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,49%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,07%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>14386</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>9170</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>21315</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>9111</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>21078</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>6,94%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10,28%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>9240</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>4955</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>15471</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,49%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16563</t>
+          <t>16441</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32377</t>
+          <t>33063</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>196496</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>191181</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>200738</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,51%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>92,93%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,57%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>193034</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>186105</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>198250</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>186342</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>198309</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>93,06%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>89,72%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,58%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>196496</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>190265</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>200781</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,51%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>380779</t>
+          <t>380093</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>396593</t>
+          <t>396715</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>48482</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>37665</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>59976</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,51%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5,06%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,05%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>55726</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>44619</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>68026</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>43970</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>67739</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>7,92%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>6,34%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9,67%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>48482</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>38294</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>60359</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>6,51%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>89092</t>
+          <t>87932</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>121457</t>
+          <t>121156</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>995</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>696362</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>684868</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>707179</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>93,49%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>91,95%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>94,94%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>975</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>648028</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>635728</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>659135</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>636015</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>659784</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>92,08%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>90,33%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>93,66%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>995</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>696362</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>684485</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>706550</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>93,49%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1327141</t>
+          <t>1327442</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1359506</t>
+          <t>1360666</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,93%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1060</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>703754</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>703754</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>703754</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8367</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4227</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14212</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6,65%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>11,29%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>8853</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5289</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>14408</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,55%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,51%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,29%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8855</t>
+          <t>9096</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4888</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15693</t>
+          <t>15156</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>17707</t>
+          <t>17463</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11894</t>
+          <t>11917</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25600</t>
+          <t>25405</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>117539</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>111694</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>121679</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>93,35%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>88,71%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,64%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>108427</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>102872</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>111991</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>92,45%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>87,71%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>95,49%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>131557</t>
+          <t>111975</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>124719</t>
+          <t>105915</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>135524</t>
+          <t>115870</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>239986</t>
+          <t>229514</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>232093</t>
+          <t>221572</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>245799</t>
+          <t>235060</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,18%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16306</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11268</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>24473</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,87%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,75%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10,32%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>13592</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8749</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>20346</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>7,13%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10,68%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17222</t>
+          <t>12725</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11141</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25084</t>
+          <t>19791</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>30814</t>
+          <t>29031</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23044</t>
+          <t>22400</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41406</t>
+          <t>38410</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>220900</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>212733</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>225938</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>93,13%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>89,68%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,25%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>176920</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>170166</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>181763</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>92,87%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>89,32%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,41%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>237813</t>
+          <t>171688</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>229951</t>
+          <t>164622</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>243894</t>
+          <t>176112</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>414734</t>
+          <t>392588</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>404142</t>
+          <t>383209</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>422504</t>
+          <t>399219</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,69%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15483</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9481</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>25763</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9,2%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5,63%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>15,3%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>14514</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8279</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>22488</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,66%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,37%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,86%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>16077</t>
+          <t>14649</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9172</t>
+          <t>9119</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25506</t>
+          <t>21887</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>30592</t>
+          <t>30132</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21048</t>
+          <t>21151</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43627</t>
+          <t>41126</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>152858</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>142578</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>158860</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>90,8%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>84,7%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>94,37%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>175071</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>167097</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>181306</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>92,34%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>88,14%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>95,63%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>169209</t>
+          <t>141555</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>159780</t>
+          <t>134317</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>176114</t>
+          <t>147085</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>344279</t>
+          <t>294413</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>331244</t>
+          <t>283419</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>353823</t>
+          <t>303394</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>93,48%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>374871</t>
+          <t>324545</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>374871</t>
+          <t>324545</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>374871</t>
+          <t>324545</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15249</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10295</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>22116</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6,08%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>13,06%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>10313</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5999</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>16051</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>6,14%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9,56%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16950</t>
+          <t>10178</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10961</t>
+          <t>6135</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24967</t>
+          <t>16248</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>27263</t>
+          <t>25427</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19742</t>
+          <t>18650</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36971</t>
+          <t>33949</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>154127</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>147260</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>159081</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>91,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>86,94%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>93,92%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>157649</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>151911</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>161963</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>93,86%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>90,44%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,43%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>164288</t>
+          <t>156967</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>156271</t>
+          <t>150897</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>170277</t>
+          <t>161010</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>321938</t>
+          <t>311094</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>312230</t>
+          <t>302572</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>329459</t>
+          <t>317871</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,46%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>55404</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>43666</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>70112</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7,91%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>6,23%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>47272</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>37016</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>58539</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>7,1%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,56%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>8,8%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>59103</t>
+          <t>46649</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45885</t>
+          <t>36345</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72733</t>
+          <t>59025</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>106375</t>
+          <t>102053</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>90023</t>
+          <t>85971</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>125932</t>
+          <t>120273</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>645425</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>630717</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>657163</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>92,09%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>90,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>93,77%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>865</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>618068</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>606801</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>628324</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>92,9%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>91,2%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>94,44%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>897</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>702869</t>
+          <t>582184</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>689239</t>
+          <t>569808</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>716087</t>
+          <t>592488</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1320937</t>
+          <t>1227609</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1301380</t>
+          <t>1209389</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1337289</t>
+          <t>1243691</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,53%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1427312</t>
+          <t>1329662</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1427312</t>
+          <t>1329662</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1427312</t>
+          <t>1329662</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
